--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97418</v>
+        <v>97419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97419</v>
+        <v>97436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96034</v>
+        <v>96051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758826</v>
       </c>
       <c r="B2" t="n">
-        <v>96427</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129758678</v>
       </c>
       <c r="B3" t="n">
-        <v>97452</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129758694</v>
       </c>
       <c r="B4" t="n">
-        <v>96067</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55111-2025 artfynd.xlsx
+++ b/artfynd/A 55111-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129758826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129758678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129758694</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>